--- a/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -67,82 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
     <t>KAREN</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
   </si>
 </sst>
 </file>
@@ -608,16 +539,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -673,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>41.94</v>
+        <v>70.97</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -692,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -724,16 +658,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920257</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -743,190 +677,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920237</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920234</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920241</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920250</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920251</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920375</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920257</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920259</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
@@ -67,13 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>KAREN</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
   </si>
 </sst>
 </file>
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
         <v>6.8</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920257</v>
+        <v>22330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -676,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
+++ b/docentes/Valerio González Valeria - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -67,10 +67,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
   </si>
   <si>
     <t>BRENDA JANELY</t>
@@ -626,7 +635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -658,16 +667,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920259</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -676,6 +685,29 @@
         <v>9</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920259</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
